--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\StockSillines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD4A6F2-08ED-49A3-B45E-E3E457FE62AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0B4E39-DC53-416F-BC54-143B9455070E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D851312-97C7-4CB6-B791-38074B5B50D6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="26">
   <si>
     <t>T0</t>
   </si>
@@ -99,18 +99,34 @@
   </si>
   <si>
     <t>YPF</t>
+  </si>
+  <si>
+    <t>SWI</t>
+  </si>
+  <si>
+    <t>Volume M</t>
+  </si>
+  <si>
+    <t>% of Shares</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>exp return</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +135,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -149,7 +173,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +182,14 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -495,12 +527,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B80EC1E3-495E-46F5-A91B-73AA1B4D51BC}">
-  <dimension ref="C2:AJ15"/>
+  <dimension ref="C2:AJ32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="7.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
     <col min="17" max="17" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
@@ -1234,6 +1268,238 @@
         <v>159.52000000000001</v>
       </c>
     </row>
+    <row r="18" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>14.305099999999999</v>
+      </c>
+      <c r="L19" s="4">
+        <v>38.975790000000003</v>
+      </c>
+      <c r="P19" s="9">
+        <f>L19/173.13</f>
+        <v>0.22512441517934503</v>
+      </c>
+    </row>
+    <row r="20" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
+        <v>13.886480000000001</v>
+      </c>
+      <c r="L20" s="4">
+        <v>11.9298</v>
+      </c>
+      <c r="M20" s="1">
+        <f>(K20-K19)/(K20+K19)/2</f>
+        <v>-7.4245572614234263E-3</v>
+      </c>
+      <c r="N20" s="1">
+        <f>(L20-L19)/(L20+L19)/2</f>
+        <v>-0.26564852700852698</v>
+      </c>
+      <c r="O20" s="2">
+        <f>ABS(N20/M20)</f>
+        <v>35.779712871067169</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" ref="P20:P24" si="12">L20/173.13</f>
+        <v>6.8906601975394222E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="3">
+        <v>16.249659999999999</v>
+      </c>
+      <c r="L21" s="4">
+        <v>3.2824499999999999</v>
+      </c>
+      <c r="M21" s="1">
+        <f t="shared" ref="M21:M23" si="13">(K21-K20)/(K21+K20)/2</f>
+        <v>3.9208405588771457E-2</v>
+      </c>
+      <c r="N21" s="1">
+        <f t="shared" ref="N21:N24" si="14">(L21-L20)/(L21+L20)/2</f>
+        <v>-0.28422324113789871</v>
+      </c>
+      <c r="O21" s="2">
+        <f>ABS(N21/M21)</f>
+        <v>7.2490384872802593</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="12"/>
+        <v>1.8959452434586726E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
+        <v>8.6189</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1.7464999999999999</v>
+      </c>
+      <c r="M22" s="1">
+        <f t="shared" si="13"/>
+        <v>-0.15342183061665007</v>
+      </c>
+      <c r="N22" s="1">
+        <f t="shared" si="14"/>
+        <v>-0.15271080444227919</v>
+      </c>
+      <c r="O22" s="2">
+        <f>ABS(N22/M22)</f>
+        <v>0.99536554757876994</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="12"/>
+        <v>1.0087795298330733E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J23" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="3">
+        <v>11.93</v>
+      </c>
+      <c r="L23" s="4">
+        <v>2.2433000000000001</v>
+      </c>
+      <c r="M23" s="1">
+        <f t="shared" si="13"/>
+        <v>8.056635634997493E-2</v>
+      </c>
+      <c r="N23" s="1">
+        <f t="shared" si="14"/>
+        <v>6.2258759837585866E-2</v>
+      </c>
+      <c r="O23" s="2">
+        <f>ABS(N23/M23)</f>
+        <v>0.77276375224340454</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="12"/>
+        <v>1.295731531219315E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J24" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="5">
+        <f>K23*(1+M24)</f>
+        <v>27.508234003738558</v>
+      </c>
+      <c r="L24" s="4">
+        <v>10</v>
+      </c>
+      <c r="M24" s="1">
+        <f>N24*O24</f>
+        <v>1.3058033532052438</v>
+      </c>
+      <c r="N24" s="1">
+        <f t="shared" si="14"/>
+        <v>0.31677325557651942</v>
+      </c>
+      <c r="O24" s="2">
+        <f>MEDIAN(O20:O23)</f>
+        <v>4.1222020174295153</v>
+      </c>
+      <c r="P24" s="9">
+        <f>MEDIAN(P20:P23)</f>
+        <v>1.5958383873389936E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J27" t="s">
+        <v>14</v>
+      </c>
+      <c r="K27" s="5">
+        <v>24.69</v>
+      </c>
+    </row>
+    <row r="28" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="5">
+        <v>29.66</v>
+      </c>
+    </row>
+    <row r="29" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="5">
+        <v>27.57</v>
+      </c>
+    </row>
+    <row r="30" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="8">
+        <f>AVERAGE(K26:K29)</f>
+        <v>26.229999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J31" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="5">
+        <v>18.37</v>
+      </c>
+    </row>
+    <row r="32" spans="10:16" x14ac:dyDescent="0.25">
+      <c r="J32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="7">
+        <f>K30/K31-1</f>
+        <v>0.42787152966793651</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
